--- a/resources/excel_tables/monster.xlsx
+++ b/resources/excel_tables/monster.xlsx
@@ -1,38 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1" state="visible"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="true"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>野狼</t>
-  </si>
-  <si>
-    <t>[1002,1003]</t>
-  </si>
-  <si>
-    <t>野猪</t>
-  </si>
-  <si>
-    <t>[1003,1004]</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
@@ -64,12 +47,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -142,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -425,196 +408,580 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>MonsterID</t>
+          <t>monster_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>level</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>mp</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>attack_range</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>DropItemRate</t>
+          <t>aggro_range</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>DropItems</t>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>drop_items</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>respawn_time</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ai_type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>attack_type</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>element_type</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2001</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TestMonster</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1,2,3</t>
+          <t>竹叶青蛇</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1001,1;1002,1</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>青竹山上的普通蛇类，毒性较弱</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>竹鼠</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>80</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>18</v>
-      </c>
-      <c r="G3">
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G3" t="n">
         <v>8</v>
       </c>
-      <c r="H3">
-        <v>120</v>
-      </c>
-      <c r="I3">
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="n">
         <v>25</v>
       </c>
-      <c r="J3">
-        <v>0.15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1</v>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1003,1;1004,1</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>以竹子为食的啮齿动物，性格温顺</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>青竹精</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1005,1;1006,1</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ranged</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>吸收了天地灵气的竹子精怪，会使用木系法术</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>竹笋怪</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>180</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>35</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1007,1;1008,1</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>35</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>passive</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>变异的竹笋，具有攻击性</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>剑灵</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" t="n">
+        <v>150</v>
+      </c>
+      <c r="F6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>120</v>
-      </c>
-      <c r="E4">
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>25</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1015,1;1016,1</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>80</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ranged</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>metal</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>剑冢中凝聚的剑灵，攻击力强大</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>毒蜘蛛</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1019,1;1020,1</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>苗寨附近的毒蜘蛛，会织网捕猎</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>蛊虫</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" t="n">
+        <v>280</v>
+      </c>
+      <c r="E8" t="n">
         <v>40</v>
       </c>
-      <c r="F4">
-        <v>22</v>
-      </c>
-      <c r="G4">
-        <v>12</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4">
-        <v>35</v>
-      </c>
-      <c r="J4">
-        <v>0.2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>3</v>
+      <c r="F8" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1023,1;1024,1</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>45</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>melee</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>蛊王洞中培育的蛊虫，毒性极强</t>
+        </is>
       </c>
     </row>
   </sheetData>
